--- a/data/trans_camb/P37-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P37-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,44; 12,65</t>
+          <t>4,08; 12,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,04; 11,55</t>
+          <t>2,82; 11,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23,6; 33,24</t>
+          <t>22,89; 33,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 7,46</t>
+          <t>0,42; 7,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,5; 9,82</t>
+          <t>2,18; 9,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,33; 38,78</t>
+          <t>31,2; 38,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,98; 8,6</t>
+          <t>3,13; 8,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,61; 9,53</t>
+          <t>3,3; 9,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>29,41; 35,25</t>
+          <t>29,32; 35,38</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,72; 50,95</t>
+          <t>13,92; 52,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,06; 46,36</t>
+          <t>8,95; 46,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82,61; 132,92</t>
+          <t>79,92; 132,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 26,86</t>
+          <t>1,31; 28,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,97; 35,08</t>
+          <t>7,0; 35,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>98,5; 140,48</t>
+          <t>98,39; 139,68</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,83; 31,76</t>
+          <t>10,64; 32,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,93; 35,23</t>
+          <t>11,28; 33,61</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>98,09; 131,71</t>
+          <t>98,74; 131,57</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,81; 5,53</t>
+          <t>1,74; 5,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,73; 5,35</t>
+          <t>1,6; 5,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,74; 18,61</t>
+          <t>8,55; 18,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,59; 4,59</t>
+          <t>0,7; 4,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,96; 5,96</t>
+          <t>2,01; 5,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,81; 44,35</t>
+          <t>18,93; 43,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,88; 4,58</t>
+          <t>1,87; 4,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,3; 5,07</t>
+          <t>2,36; 5,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,16; 31,54</t>
+          <t>15,98; 31,8</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>22,57; 90,69</t>
+          <t>21,39; 91,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>22,19; 88,43</t>
+          <t>19,6; 88,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>120,77; 297,65</t>
+          <t>127,69; 293,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,39; 83,65</t>
+          <t>9,5; 83,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,11; 111,58</t>
+          <t>26,15; 105,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>279,49; 788,37</t>
+          <t>282,28; 796,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,84; 76,24</t>
+          <t>25,39; 76,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>31,44; 85,13</t>
+          <t>31,44; 83,79</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>233,69; 492,86</t>
+          <t>230,1; 482,8</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 3,93</t>
+          <t>-4,62; 4,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 3,39</t>
+          <t>-4,78; 3,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17,16; 26,65</t>
+          <t>17,45; 26,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 3,75</t>
+          <t>-4,15; 4,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 4,37</t>
+          <t>-3,26; 4,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,33; 25,27</t>
+          <t>16,88; 25,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 2,63</t>
+          <t>-3,21; 2,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 2,75</t>
+          <t>-2,74; 2,82</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>18,48; 24,96</t>
+          <t>18,69; 24,83</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-34,76; 40,27</t>
+          <t>-34,62; 45,95</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-33,98; 36,29</t>
+          <t>-36,71; 36,8</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>121,76; 283,56</t>
+          <t>125,31; 289,09</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-38,94; 50,42</t>
+          <t>-36,71; 55,55</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-31,43; 60,55</t>
+          <t>-29,18; 55,93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>136,49; 342,4</t>
+          <t>140,14; 344,39</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-28,38; 27,78</t>
+          <t>-28,23; 25,7</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-23,98; 30,3</t>
+          <t>-22,74; 31,26</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>152,96; 277,67</t>
+          <t>152,8; 276,94</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,98; 5,58</t>
+          <t>2,13; 5,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,03; 3,59</t>
+          <t>0,17; 3,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,0; 18,14</t>
+          <t>8,95; 18,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,66; 4,32</t>
+          <t>0,51; 4,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 3,37</t>
+          <t>-0,38; 3,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,83; 34,84</t>
+          <t>18,81; 35,1</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,35</t>
+          <t>1,84; 4,44</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,89</t>
+          <t>0,39; 2,87</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>15,62; 25,68</t>
+          <t>15,53; 25,71</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>13,27; 42,84</t>
+          <t>14,62; 43,16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,49; 27,76</t>
+          <t>1,13; 27,91</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>66,03; 136,2</t>
+          <t>63,17; 135,64</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,03; 28,71</t>
+          <t>3,09; 29,28</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 22,21</t>
+          <t>-2,24; 22,81</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>115,67; 222,43</t>
+          <t>116,92; 230,65</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,51; 30,56</t>
+          <t>11,9; 31,05</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,36; 20,21</t>
+          <t>2,51; 20,34</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>103,52; 173,77</t>
+          <t>102,83; 172,93</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P37-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P37-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28,0</t>
+          <t>25,39</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,14</t>
+          <t>34,86</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>32,35</t>
+          <t>31,03</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,08; 12,81</t>
+          <t>4,25; 12,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,82; 11,61</t>
+          <t>3,23; 11,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22,89; 33,22</t>
+          <t>20,64; 30,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,42; 7,83</t>
+          <t>0,19; 7,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,18; 9,95</t>
+          <t>1,5; 9,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,2; 38,7</t>
+          <t>31,42; 38,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,13; 8,68</t>
+          <t>3,18; 8,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,3; 9,18</t>
+          <t>3,45; 9,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>29,32; 35,38</t>
+          <t>27,99; 34,12</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>105,26%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>118,33%</t>
+          <t>117,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>114,15%</t>
+          <t>109,49%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,92; 52,03</t>
+          <t>15,15; 49,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,95; 46,17</t>
+          <t>11,47; 46,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>79,92; 132,18</t>
+          <t>72,37; 121,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,31; 28,1</t>
+          <t>0,53; 25,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,0; 35,41</t>
+          <t>4,74; 34,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>98,39; 139,68</t>
+          <t>97,79; 138,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,64; 32,07</t>
+          <t>10,82; 31,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,28; 33,61</t>
+          <t>11,83; 34,47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>98,74; 131,57</t>
+          <t>94,49; 127,29</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15,08</t>
+          <t>17,87</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,45</t>
+          <t>20,52</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>20,69</t>
+          <t>19,17</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,74; 5,6</t>
+          <t>1,83; 5,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,6; 5,31</t>
+          <t>1,38; 5,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,55; 18,36</t>
+          <t>15,55; 20,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,7; 4,51</t>
+          <t>0,81; 4,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,01; 5,94</t>
+          <t>1,84; 5,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,93; 43,63</t>
+          <t>18,35; 22,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,87; 4,59</t>
+          <t>1,87; 4,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,36; 5,01</t>
+          <t>2,5; 5,02</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15,98; 31,8</t>
+          <t>17,7; 20,81</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>217,53%</t>
+          <t>257,78%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>419,57%</t>
+          <t>325,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>312,18%</t>
+          <t>289,24%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,39; 91,69</t>
+          <t>22,3; 90,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19,6; 88,59</t>
+          <t>17,07; 86,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>127,69; 293,05</t>
+          <t>189,88; 327,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,5; 83,37</t>
+          <t>10,7; 84,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>26,15; 105,75</t>
+          <t>24,85; 109,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>282,28; 796,99</t>
+          <t>242,19; 418,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,39; 76,94</t>
+          <t>24,81; 76,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>31,44; 83,79</t>
+          <t>34,93; 84,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>230,1; 482,8</t>
+          <t>238,84; 353,4</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21,94</t>
+          <t>21,48</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21,5</t>
+          <t>21,61</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>21,64</t>
+          <t>21,46</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 4,05</t>
+          <t>-4,61; 4,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 3,49</t>
+          <t>-4,53; 3,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17,45; 26,78</t>
+          <t>16,82; 25,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 4,24</t>
+          <t>-4,7; 3,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 4,14</t>
+          <t>-3,24; 4,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,88; 25,41</t>
+          <t>17,46; 25,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 2,44</t>
+          <t>-3,63; 2,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 2,82</t>
+          <t>-2,95; 2,82</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>18,69; 24,83</t>
+          <t>18,27; 24,54</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>192,71%</t>
+          <t>188,66%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>228,54%</t>
+          <t>229,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>206,68%</t>
+          <t>204,98%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-34,62; 45,95</t>
+          <t>-34,79; 42,16</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-36,71; 36,8</t>
+          <t>-34,31; 33,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>125,31; 289,09</t>
+          <t>122,59; 287,5</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-36,71; 55,55</t>
+          <t>-40,46; 51,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-29,18; 55,93</t>
+          <t>-27,62; 66,19</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>140,14; 344,39</t>
+          <t>141,86; 349,35</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-28,23; 25,7</t>
+          <t>-30,18; 25,95</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-22,74; 31,26</t>
+          <t>-25,55; 29,96</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>152,8; 276,94</t>
+          <t>151,33; 281,0</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15,11</t>
+          <t>17,02</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,18</t>
+          <t>20,11</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>19,27</t>
+          <t>18,62</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,13; 5,54</t>
+          <t>2,11; 5,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,17; 3,62</t>
+          <t>0,1; 3,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,95; 18,0</t>
+          <t>15,06; 19,04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,28</t>
+          <t>0,52; 4,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 3,37</t>
+          <t>-0,46; 3,4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,81; 35,1</t>
+          <t>18,24; 21,97</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,44</t>
+          <t>1,82; 4,24</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,87</t>
+          <t>0,23; 2,96</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>15,53; 25,71</t>
+          <t>17,31; 20,13</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>108,91%</t>
+          <t>122,64%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>146,26%</t>
+          <t>126,88%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>129,53%</t>
+          <t>125,16%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>14,62; 43,16</t>
+          <t>14,3; 43,13</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,13; 27,91</t>
+          <t>0,72; 28,33</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>63,17; 135,64</t>
+          <t>102,14; 146,16</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,09; 29,28</t>
+          <t>2,83; 29,26</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 22,81</t>
+          <t>-2,86; 22,39</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>116,92; 230,65</t>
+          <t>107,81; 147,72</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,9; 31,05</t>
+          <t>11,79; 30,06</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,51; 20,34</t>
+          <t>1,45; 20,52</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>102,83; 172,93</t>
+          <t>110,31; 141,37</t>
         </is>
       </c>
     </row>
